--- a/dtm_dashboard/excel_data/keeping_prr/Новикова-прибоя/Апрель 2026.xlsx
+++ b/dtm_dashboard/excel_data/keeping_prr/Новикова-прибоя/Апрель 2026.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 19.04.2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t>Остатки и обороты в тоннах по дням с 01.04.2026 по 30.04.2026</t>
   </si>
   <si>
     <t>Отбор:</t>
@@ -107,6 +107,39 @@
   </si>
   <si>
     <t>19.04.2026</t>
+  </si>
+  <si>
+    <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>21.04.2026</t>
+  </si>
+  <si>
+    <t>22.04.2026</t>
+  </si>
+  <si>
+    <t>23.04.2026</t>
+  </si>
+  <si>
+    <t>24.04.2026</t>
+  </si>
+  <si>
+    <t>25.04.2026</t>
+  </si>
+  <si>
+    <t>26.04.2026</t>
+  </si>
+  <si>
+    <t>27.04.2026</t>
+  </si>
+  <si>
+    <t>28.04.2026</t>
+  </si>
+  <si>
+    <t>29.04.2026</t>
+  </si>
+  <si>
+    <t>30.04.2026</t>
   </si>
   <si>
     <t>Итого</t>
@@ -116,12 +149,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="50" formatCode=""/>
     <numFmt numFmtId="51" formatCode="0.000"/>
     <numFmt numFmtId="52" formatCode="0.0"/>
     <numFmt numFmtId="53" formatCode="#,##0.000"/>
-    <numFmt numFmtId="54" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -269,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -310,10 +342,13 @@
     <xf numFmtId="53" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
+    <xf numFmtId="2" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="top" wrapText="0"/>
+    </xf>
     <xf fontId="3" fillId="2" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="54" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
     <xf fontId="3" fillId="2" borderId="5" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -322,13 +357,7 @@
     <xf fontId="3" fillId="2" borderId="6" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="top" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="5" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="top" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="6" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="51" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -350,19 +379,19 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="J26"/>
+  <dimension ref="J37"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="8.66796875" style="1" customWidth="true"/>
     <col min="2" max="2" width="1.83203125" style="1" customWidth="true"/>
     <col min="3" max="3" width="3.5" style="1" customWidth="true"/>
-    <col min="4" max="4" width="11" style="1" customWidth="true"/>
-    <col min="5" max="5" width="10.83203125" style="1" customWidth="true"/>
-    <col min="6" max="6" width="9" style="1" customWidth="true"/>
-    <col min="7" max="7" width="3.83203125" style="1" customWidth="true"/>
+    <col min="4" max="4" width="11.16796875" style="1" customWidth="true"/>
+    <col min="5" max="5" width="11.16796875" style="1" customWidth="true"/>
+    <col min="6" max="6" width="8.66796875" style="1" customWidth="true"/>
+    <col min="7" max="7" width="4.16796875" style="1" customWidth="true"/>
     <col min="8" max="8" width="19.33203125" style="1" customWidth="true"/>
-    <col min="9" max="9" width="2.16796875" style="1" customWidth="true"/>
-    <col min="10" max="10" width="17" style="1" customWidth="true"/>
+    <col min="9" max="9" width="1.83203125" style="1" customWidth="true"/>
+    <col min="10" max="10" width="17.5" style="1" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="true" s="1" customFormat="true"/>
@@ -789,26 +818,250 @@
       <c r="I25" s="10" t="e"/>
       <c r="J25" s="11" t="e"/>
     </row>
-    <row r="26" ht="13" customHeight="true">
-      <c r="A26" s="14" t="s">
+    <row r="26" ht="11" customHeight="true">
+      <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="14" t="e"/>
-      <c r="C26" s="14" t="e"/>
-      <c r="D26" s="15" t="n">
-        <v>3559.5</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>1365.6</v>
-      </c>
-      <c r="F26" s="16" t="e"/>
-      <c r="G26" s="17" t="e"/>
-      <c r="H26" s="18" t="e"/>
-      <c r="I26" s="19" t="e"/>
-      <c r="J26" s="20" t="e"/>
+      <c r="B26" s="5" t="e"/>
+      <c r="C26" s="5" t="e"/>
+      <c r="D26" s="12" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>7085.945</v>
+      </c>
+      <c r="G26" s="13" t="e"/>
+      <c r="H26" s="9" t="e"/>
+      <c r="I26" s="10" t="e"/>
+      <c r="J26" s="11" t="e"/>
+    </row>
+    <row r="27" ht="11" customHeight="true">
+      <c r="A27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="5" t="e"/>
+      <c r="C27" s="5" t="e"/>
+      <c r="D27" s="14" t="n">
+        <v>334.25</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>7419.895</v>
+      </c>
+      <c r="G27" s="13" t="e"/>
+      <c r="H27" s="7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J27" s="7" t="e"/>
+    </row>
+    <row r="28" ht="11" customHeight="true">
+      <c r="A28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="5" t="e"/>
+      <c r="C28" s="5" t="e"/>
+      <c r="D28" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>7420.395</v>
+      </c>
+      <c r="G28" s="13" t="e"/>
+      <c r="H28" s="9" t="e"/>
+      <c r="I28" s="10" t="e"/>
+      <c r="J28" s="11" t="e"/>
+    </row>
+    <row r="29" ht="11" customHeight="true">
+      <c r="A29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="5" t="e"/>
+      <c r="C29" s="5" t="e"/>
+      <c r="D29" s="12" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="E29" s="9" t="e"/>
+      <c r="F29" s="13" t="n">
+        <v>7576.895</v>
+      </c>
+      <c r="G29" s="13" t="e"/>
+      <c r="H29" s="9" t="e"/>
+      <c r="I29" s="10" t="e"/>
+      <c r="J29" s="11" t="e"/>
+    </row>
+    <row r="30" ht="11" customHeight="true">
+      <c r="A30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="5" t="e"/>
+      <c r="C30" s="5" t="e"/>
+      <c r="D30" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>7643.695</v>
+      </c>
+      <c r="G30" s="13" t="e"/>
+      <c r="H30" s="9" t="e"/>
+      <c r="I30" s="10" t="e"/>
+      <c r="J30" s="11" t="e"/>
+    </row>
+    <row r="31" ht="11" customHeight="true">
+      <c r="A31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="5" t="e"/>
+      <c r="C31" s="5" t="e"/>
+      <c r="D31" s="12" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>7667.195</v>
+      </c>
+      <c r="G31" s="13" t="e"/>
+      <c r="H31" s="9" t="e"/>
+      <c r="I31" s="10" t="e"/>
+      <c r="J31" s="11" t="e"/>
+    </row>
+    <row r="32" ht="11" customHeight="true">
+      <c r="A32" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="5" t="e"/>
+      <c r="C32" s="5" t="e"/>
+      <c r="D32" s="9" t="e"/>
+      <c r="E32" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>7623.195</v>
+      </c>
+      <c r="G32" s="13" t="e"/>
+      <c r="H32" s="9" t="e"/>
+      <c r="I32" s="10" t="e"/>
+      <c r="J32" s="11" t="e"/>
+    </row>
+    <row r="33" ht="11" customHeight="true">
+      <c r="A33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="5" t="e"/>
+      <c r="C33" s="5" t="e"/>
+      <c r="D33" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>7623.695</v>
+      </c>
+      <c r="G33" s="13" t="e"/>
+      <c r="H33" s="9" t="e"/>
+      <c r="I33" s="10" t="e"/>
+      <c r="J33" s="11" t="e"/>
+    </row>
+    <row r="34" ht="11" customHeight="true">
+      <c r="A34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="5" t="e"/>
+      <c r="C34" s="5" t="e"/>
+      <c r="D34" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>7779.695</v>
+      </c>
+      <c r="G34" s="13" t="e"/>
+      <c r="H34" s="9" t="e"/>
+      <c r="I34" s="10" t="e"/>
+      <c r="J34" s="11" t="e"/>
+    </row>
+    <row r="35" ht="11" customHeight="true">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="e"/>
+      <c r="C35" s="5" t="e"/>
+      <c r="D35" s="12" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>7865.945</v>
+      </c>
+      <c r="G35" s="13" t="e"/>
+      <c r="H35" s="9" t="e"/>
+      <c r="I35" s="10" t="e"/>
+      <c r="J35" s="11" t="e"/>
+    </row>
+    <row r="36" ht="11" customHeight="true">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="e"/>
+      <c r="C36" s="5" t="e"/>
+      <c r="D36" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>7953.445</v>
+      </c>
+      <c r="G36" s="13" t="e"/>
+      <c r="H36" s="9" t="e"/>
+      <c r="I36" s="10" t="e"/>
+      <c r="J36" s="11" t="e"/>
+    </row>
+    <row r="37" ht="13" customHeight="true">
+      <c r="A37" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="15" t="e"/>
+      <c r="C37" s="15" t="e"/>
+      <c r="D37" s="16" t="n">
+        <v>5006.75</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>1835.85</v>
+      </c>
+      <c r="F37" s="17" t="e"/>
+      <c r="G37" s="18" t="e"/>
+      <c r="H37" s="19" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="I37" s="19" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J37" s="19" t="e"/>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="66">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="I6:J6"/>
@@ -851,6 +1104,30 @@
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="A26:C26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="I37:J37"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait"/>
